--- a/backend/data/financials_by_company/1915.HK.xlsx
+++ b/backend/data/financials_by_company/1915.HK.xlsx
@@ -597,40 +597,40 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-22443.444479</v>
+        <v>2840.66637</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1955</v>
+        <v>0.288393</v>
       </c>
       <c r="D2" t="n">
-        <v>-114800</v>
+        <v>9850</v>
       </c>
       <c r="E2" t="n">
-        <v>-114800</v>
+        <v>9850</v>
       </c>
       <c r="F2" t="n">
-        <v>-8232972</v>
+        <v>4560888</v>
       </c>
       <c r="G2" t="n">
-        <v>1528364</v>
+        <v>1998504</v>
       </c>
       <c r="H2" t="n">
-        <v>52197157</v>
+        <v>60345687</v>
       </c>
       <c r="I2" t="n">
-        <v>20476</v>
+        <v>200093</v>
       </c>
       <c r="J2" t="n">
-        <v>52217633</v>
+        <v>60545780</v>
       </c>
       <c r="K2" t="n">
-        <v>-8140615.444479</v>
+        <v>4553878.66637</v>
       </c>
       <c r="L2" t="n">
-        <v>-8232972</v>
+        <v>4560888</v>
       </c>
       <c r="M2" t="n">
         <v>600000000</v>
@@ -639,67 +639,67 @@
         <v>600000000</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>-8232972</v>
+        <v>4560888</v>
       </c>
       <c r="R2" t="n">
-        <v>-8232972</v>
+        <v>4560888</v>
       </c>
       <c r="S2" t="n">
-        <v>-8232972</v>
+        <v>4560888</v>
       </c>
       <c r="T2" t="n">
-        <v>127643</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-8360615</v>
+        <v>4560888</v>
       </c>
       <c r="V2" t="n">
-        <v>-8360615</v>
+        <v>4560888</v>
       </c>
       <c r="W2" t="n">
-        <v>-2031702</v>
+        <v>1848387</v>
       </c>
       <c r="X2" t="n">
-        <v>-10392317</v>
+        <v>6409275</v>
       </c>
       <c r="Y2" t="n">
-        <v>-114800</v>
+        <v>9850</v>
       </c>
       <c r="Z2" t="n">
-        <v>114800</v>
+        <v>-9850</v>
       </c>
       <c r="AA2" t="n">
-        <v>8910489</v>
+        <v>9559202</v>
       </c>
       <c r="AB2" t="n">
-        <v>309462</v>
+        <v>396103</v>
       </c>
       <c r="AC2" t="n">
-        <v>1528364</v>
+        <v>1998504</v>
       </c>
       <c r="AD2" t="n">
-        <v>1528364</v>
+        <v>1998504</v>
       </c>
       <c r="AE2" t="n">
-        <v>3846598</v>
+        <v>3239701</v>
       </c>
       <c r="AF2" t="n">
-        <v>315537</v>
+        <v>155474</v>
       </c>
       <c r="AG2" t="n">
-        <v>3531061</v>
+        <v>3084227</v>
       </c>
       <c r="AH2" t="n">
-        <v>52401138</v>
+        <v>62534012</v>
       </c>
       <c r="AI2" t="n">
-        <v>52401138</v>
+        <v>62534012</v>
       </c>
     </row>
     <row r="3">
@@ -811,40 +811,40 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>2840.66637</v>
+        <v>-22443.444479</v>
       </c>
       <c r="C4" t="n">
-        <v>0.288393</v>
+        <v>0.1955</v>
       </c>
       <c r="D4" t="n">
-        <v>9850</v>
+        <v>-114800</v>
       </c>
       <c r="E4" t="n">
-        <v>9850</v>
+        <v>-114800</v>
       </c>
       <c r="F4" t="n">
-        <v>4560888</v>
+        <v>-8232972</v>
       </c>
       <c r="G4" t="n">
-        <v>1998504</v>
+        <v>1528364</v>
       </c>
       <c r="H4" t="n">
-        <v>60345687</v>
+        <v>52197157</v>
       </c>
       <c r="I4" t="n">
-        <v>200093</v>
+        <v>20476</v>
       </c>
       <c r="J4" t="n">
-        <v>60545780</v>
+        <v>52217633</v>
       </c>
       <c r="K4" t="n">
-        <v>4553878.66637</v>
+        <v>-8140615.444479</v>
       </c>
       <c r="L4" t="n">
-        <v>4560888</v>
+        <v>-8232972</v>
       </c>
       <c r="M4" t="n">
         <v>600000000</v>
@@ -853,67 +853,67 @@
         <v>600000000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>4560888</v>
+        <v>-8232972</v>
       </c>
       <c r="R4" t="n">
-        <v>4560888</v>
+        <v>-8232972</v>
       </c>
       <c r="S4" t="n">
-        <v>4560888</v>
+        <v>-8232972</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>127643</v>
       </c>
       <c r="U4" t="n">
-        <v>4560888</v>
+        <v>-8360615</v>
       </c>
       <c r="V4" t="n">
-        <v>4560888</v>
+        <v>-8360615</v>
       </c>
       <c r="W4" t="n">
-        <v>1848387</v>
+        <v>-2031702</v>
       </c>
       <c r="X4" t="n">
-        <v>6409275</v>
+        <v>-10392317</v>
       </c>
       <c r="Y4" t="n">
-        <v>9850</v>
+        <v>-114800</v>
       </c>
       <c r="Z4" t="n">
-        <v>-9850</v>
+        <v>114800</v>
       </c>
       <c r="AA4" t="n">
-        <v>9559202</v>
+        <v>8910489</v>
       </c>
       <c r="AB4" t="n">
-        <v>396103</v>
+        <v>309462</v>
       </c>
       <c r="AC4" t="n">
-        <v>1998504</v>
+        <v>1528364</v>
       </c>
       <c r="AD4" t="n">
-        <v>1998504</v>
+        <v>1528364</v>
       </c>
       <c r="AE4" t="n">
-        <v>3239701</v>
+        <v>3846598</v>
       </c>
       <c r="AF4" t="n">
-        <v>155474</v>
+        <v>315537</v>
       </c>
       <c r="AG4" t="n">
-        <v>3084227</v>
+        <v>3531061</v>
       </c>
       <c r="AH4" t="n">
-        <v>62534012</v>
+        <v>52401138</v>
       </c>
       <c r="AI4" t="n">
-        <v>62534012</v>
+        <v>52401138</v>
       </c>
     </row>
   </sheetData>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>600000000</v>
@@ -1128,28 +1128,28 @@
         <v>600000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1535362</v>
+        <v>2555624</v>
       </c>
       <c r="E2" t="n">
-        <v>869767001</v>
+        <v>885644105</v>
       </c>
       <c r="F2" t="n">
-        <v>869767001</v>
+        <v>885644105</v>
       </c>
       <c r="G2" t="n">
-        <v>869767001</v>
+        <v>887725847</v>
       </c>
       <c r="H2" t="n">
-        <v>871726292</v>
+        <v>887725847</v>
       </c>
       <c r="I2" t="n">
-        <v>1959291</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>869767001</v>
+        <v>887725847</v>
       </c>
       <c r="K2" t="n">
-        <v>156666255</v>
+        <v>174521164</v>
       </c>
       <c r="L2" t="n">
         <v>600000000</v>
@@ -1158,73 +1158,75 @@
         <v>600000000</v>
       </c>
       <c r="N2" t="n">
-        <v>15191353</v>
+        <v>16750551</v>
       </c>
       <c r="O2" t="n">
-        <v>1535362</v>
+        <v>2555624</v>
       </c>
       <c r="P2" t="n">
-        <v>10128820</v>
+        <v>10789188</v>
       </c>
       <c r="Q2" t="n">
-        <v>8382187</v>
+        <v>8281188</v>
       </c>
       <c r="R2" t="n">
-        <v>1746633</v>
+        <v>2508000</v>
       </c>
       <c r="S2" t="n">
-        <v>886917645</v>
+        <v>904476398</v>
       </c>
       <c r="T2" t="n">
-        <v>396063</v>
-      </c>
-      <c r="U2" t="n">
-        <v>396063</v>
-      </c>
-      <c r="V2" t="n">
-        <v>396063</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+        <v>79916885</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>79916885</v>
+      </c>
+      <c r="X2" t="n">
+        <v>79916885</v>
+      </c>
       <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>2081742</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>22628</v>
+      </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2059114</v>
       </c>
       <c r="AB2" t="n">
-        <v>1426793</v>
+        <v>5258416</v>
       </c>
       <c r="AC2" t="n">
-        <v>-16485325</v>
+        <v>-13516729</v>
       </c>
       <c r="AD2" t="n">
-        <v>17912118</v>
+        <v>18775145</v>
       </c>
       <c r="AE2" t="n">
-        <v>5300521</v>
+        <v>6160576</v>
       </c>
       <c r="AF2" t="n">
-        <v>1822718</v>
+        <v>1904135</v>
       </c>
       <c r="AG2" t="n">
-        <v>10788879</v>
+        <v>10710434</v>
       </c>
       <c r="AH2" t="n">
-        <v>58324</v>
+        <v>339929</v>
       </c>
       <c r="AI2" t="n">
-        <v>507625</v>
+        <v>846688</v>
       </c>
       <c r="AJ2" t="n">
-        <v>279027</v>
+        <v>5608151</v>
       </c>
       <c r="AK2" t="n">
-        <v>279027</v>
+        <v>5608151</v>
       </c>
       <c r="AL2" t="n">
-        <v>279027</v>
+        <v>5608151</v>
       </c>
     </row>
     <row r="3">
@@ -1345,7 +1347,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>600000000</v>
@@ -1354,28 +1356,28 @@
         <v>600000000</v>
       </c>
       <c r="D4" t="n">
-        <v>2555624</v>
+        <v>1535362</v>
       </c>
       <c r="E4" t="n">
-        <v>885644105</v>
+        <v>869767001</v>
       </c>
       <c r="F4" t="n">
-        <v>885644105</v>
+        <v>869767001</v>
       </c>
       <c r="G4" t="n">
-        <v>887725847</v>
+        <v>869767001</v>
       </c>
       <c r="H4" t="n">
-        <v>887725847</v>
+        <v>871726292</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1959291</v>
       </c>
       <c r="J4" t="n">
-        <v>887725847</v>
+        <v>869767001</v>
       </c>
       <c r="K4" t="n">
-        <v>174521164</v>
+        <v>156666255</v>
       </c>
       <c r="L4" t="n">
         <v>600000000</v>
@@ -1384,75 +1386,73 @@
         <v>600000000</v>
       </c>
       <c r="N4" t="n">
-        <v>16750551</v>
+        <v>15191353</v>
       </c>
       <c r="O4" t="n">
-        <v>2555624</v>
+        <v>1535362</v>
       </c>
       <c r="P4" t="n">
-        <v>10789188</v>
+        <v>10128820</v>
       </c>
       <c r="Q4" t="n">
-        <v>8281188</v>
+        <v>8382187</v>
       </c>
       <c r="R4" t="n">
-        <v>2508000</v>
+        <v>1746633</v>
       </c>
       <c r="S4" t="n">
-        <v>904476398</v>
+        <v>886917645</v>
       </c>
       <c r="T4" t="n">
-        <v>79916885</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>79916885</v>
-      </c>
-      <c r="X4" t="n">
-        <v>79916885</v>
-      </c>
+        <v>396063</v>
+      </c>
+      <c r="U4" t="n">
+        <v>396063</v>
+      </c>
+      <c r="V4" t="n">
+        <v>396063</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>2081742</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>22628</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>2059114</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>5258416</v>
+        <v>1426793</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13516729</v>
+        <v>-16485325</v>
       </c>
       <c r="AD4" t="n">
-        <v>18775145</v>
+        <v>17912118</v>
       </c>
       <c r="AE4" t="n">
-        <v>6160576</v>
+        <v>5300521</v>
       </c>
       <c r="AF4" t="n">
-        <v>1904135</v>
+        <v>1822718</v>
       </c>
       <c r="AG4" t="n">
-        <v>10710434</v>
+        <v>10788879</v>
       </c>
       <c r="AH4" t="n">
-        <v>339929</v>
+        <v>58324</v>
       </c>
       <c r="AI4" t="n">
-        <v>846688</v>
+        <v>507625</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5608151</v>
+        <v>279027</v>
       </c>
       <c r="AK4" t="n">
-        <v>5608151</v>
+        <v>279027</v>
       </c>
       <c r="AL4" t="n">
-        <v>5608151</v>
+        <v>279027</v>
       </c>
     </row>
   </sheetData>
@@ -1648,39 +1648,47 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-2491900</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>84677482</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-127296</v>
+      </c>
       <c r="D2" t="n">
-        <v>-37381</v>
+        <v>-860947</v>
       </c>
       <c r="E2" t="n">
-        <v>279027</v>
+        <v>5608151</v>
       </c>
       <c r="F2" t="n">
-        <v>1639818</v>
+        <v>803738</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="H2" t="n">
-        <v>-1360795</v>
+        <v>4804420</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-911442</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>-241830</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-127296</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-127296</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-127296</v>
+      </c>
       <c r="O2" t="n">
-        <v>1093724</v>
+        <v>-79822567</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -1689,59 +1697,61 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-78962120</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>1037880</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-80000000</v>
+      </c>
       <c r="U2" t="n">
-        <v>1093724</v>
+        <v>-860447</v>
       </c>
       <c r="V2" t="n">
-        <v>1131105</v>
+        <v>500</v>
       </c>
       <c r="W2" t="n">
-        <v>-37381</v>
+        <v>-860947</v>
       </c>
       <c r="X2" t="n">
-        <v>-2454519</v>
+        <v>85538429</v>
       </c>
       <c r="Y2" t="n">
-        <v>-682681</v>
+        <v>-12793789</v>
       </c>
       <c r="Z2" t="n">
-        <v>-46277234</v>
+        <v>43855914</v>
       </c>
       <c r="AA2" t="n">
-        <v>-4721256</v>
+        <v>-157497</v>
       </c>
       <c r="AB2" t="n">
-        <v>3181032</v>
+        <v>-22560</v>
       </c>
       <c r="AC2" t="n">
-        <v>-659814</v>
+        <v>-497017</v>
       </c>
       <c r="AD2" t="n">
-        <v>53768166</v>
+        <v>46492270</v>
       </c>
       <c r="AE2" t="n">
-        <v>1528364</v>
+        <v>1998504</v>
       </c>
       <c r="AF2" t="n">
-        <v>1528364</v>
+        <v>1998504</v>
       </c>
       <c r="AG2" t="n">
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
-        <v>261001</v>
+        <v>-9850</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-10392317</v>
+        <v>6409275</v>
       </c>
     </row>
     <row r="3">
@@ -1856,47 +1866,39 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>84677482</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-127296</v>
-      </c>
+        <v>-2491900</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-860947</v>
+        <v>-37381</v>
       </c>
       <c r="E4" t="n">
-        <v>5608151</v>
+        <v>279027</v>
       </c>
       <c r="F4" t="n">
-        <v>803738</v>
+        <v>1639818</v>
       </c>
       <c r="G4" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>4804420</v>
+        <v>-1360795</v>
       </c>
       <c r="I4" t="n">
-        <v>-911442</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>-241830</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-127296</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-127296</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-127296</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-79822567</v>
+        <v>1093724</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1905,61 +1907,59 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-78962120</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1037880</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-80000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>-860447</v>
+        <v>1093724</v>
       </c>
       <c r="V4" t="n">
-        <v>500</v>
+        <v>1131105</v>
       </c>
       <c r="W4" t="n">
-        <v>-860947</v>
+        <v>-37381</v>
       </c>
       <c r="X4" t="n">
-        <v>85538429</v>
+        <v>-2454519</v>
       </c>
       <c r="Y4" t="n">
-        <v>-12793789</v>
+        <v>-682681</v>
       </c>
       <c r="Z4" t="n">
-        <v>43855914</v>
+        <v>-46277234</v>
       </c>
       <c r="AA4" t="n">
-        <v>-157497</v>
+        <v>-4721256</v>
       </c>
       <c r="AB4" t="n">
-        <v>-22560</v>
+        <v>3181032</v>
       </c>
       <c r="AC4" t="n">
-        <v>-497017</v>
+        <v>-659814</v>
       </c>
       <c r="AD4" t="n">
-        <v>46492270</v>
+        <v>53768166</v>
       </c>
       <c r="AE4" t="n">
-        <v>1998504</v>
+        <v>1528364</v>
       </c>
       <c r="AF4" t="n">
-        <v>1998504</v>
+        <v>1528364</v>
       </c>
       <c r="AG4" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-9850</v>
+        <v>261001</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6409275</v>
+        <v>-10392317</v>
       </c>
     </row>
   </sheetData>
@@ -2459,187 +2459,187 @@
       </c>
       <c r="CS1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="ED1" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Li  Bai', 'age': 49, 'title': 'Chief Executive, GM &amp; Compliance Officer', 'yearBorn': 1976, 'fiscalYear': 2023, 'totalPay': 463416, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yinqing  Zhou', 'age': 46, 'title': 'Deputy GM &amp; Company Secretary', 'yearBorn': 1979, 'fiscalYear': 2023, 'totalPay': 374643, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhenyong  Tian', 'title': 'Executive Chairman', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Qian  Gu', 'title': 'Responsible Officer of the Legal Department', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhuo  Zhang', 'age': 45, 'title': 'Executive Director', 'yearBorn': 1980, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Min  Huang', 'title': 'Executive Director', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chun Hin  Chan', 'age': 32, 'title': 'Company Secretary', 'yearBorn': 1993, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Li  Bai', 'age': 49, 'title': 'Chief Executive, GM &amp; Compliance Officer', 'yearBorn': 1976, 'fiscalYear': 2023, 'totalPay': 463047, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yinqing  Zhou', 'age': 46, 'title': 'Deputy GM &amp; Company Secretary', 'yearBorn': 1979, 'fiscalYear': 2023, 'totalPay': 374345, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhenyong  Tian', 'title': 'Executive Chairman', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Qian  Gu', 'title': 'Responsible Officer of the Legal Department', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhuo  Zhang', 'age': 45, 'title': 'Executive Director', 'yearBorn': 1980, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Min  Huang', 'title': 'Executive Director', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chun Hin  Chan', 'age': 32, 'title': 'Company Secretary', 'yearBorn': 1993, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -2772,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.358</v>
+        <v>-0.37</v>
       </c>
       <c r="AF2" t="n">
         <v>9004000</v>
@@ -2858,10 +2858,10 @@
         <v>600000000</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.6569391</v>
+        <v>1.659894</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.15993345</v>
+        <v>0.15964875</v>
       </c>
       <c r="BI2" t="n">
         <v>1703980800</v>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BQ2" t="n">
         <v>0.027376</v>
@@ -2991,138 +2991,138 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
+          <t>Yangzhou Guangling District Taihe Rural Micro-finance Company Limited</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CU2" t="n">
+        <v>1743407752</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>TAIHE M-FIN</t>
+        </is>
+      </c>
+      <c r="CX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>finmb_428032063</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.030000001</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>0.26 - 0.315</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="CT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CV2" t="n">
-        <v>1743407752</v>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>finmb_428032063</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DA2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="n">
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.004999995</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.019230751</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>0.26 - 0.315</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.050000012</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.1587302</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1724404422</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1724404422</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1494207000000</v>
+      </c>
+      <c r="EC2" t="n">
         <v>-10.169493</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>TAIHE M-FIN</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>Yangzhou Guangling District Taihe Rural Micro-finance Company Limited</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.004999995</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.019230751</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>0.26 - 0.315</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.050000012</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.1587302</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1724404422</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1724404422</v>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1494207000000</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.030000001</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>0.26 - 0.315</t>
-        </is>
       </c>
       <c r="ED2" t="inlineStr"/>
     </row>
